--- a/tame_output/ON/bt/strategyON_20230830.xlsx
+++ b/tame_output/ON/bt/strategyON_20230830.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-158.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1704"/>
+  <dimension ref="A1:G1705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40702,7 +40702,7 @@
         <v>45166</v>
       </c>
       <c r="B1704" t="n">
-        <v>2.769506775385254</v>
+        <v>2.769676306134903</v>
       </c>
       <c r="C1704" t="n">
         <v>2.898149615933988</v>
@@ -40718,6 +40718,29 @@
       </c>
       <c r="G1704" t="n">
         <v>4.196992074112566</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="2" t="n">
+        <v>45167</v>
+      </c>
+      <c r="B1705" t="n">
+        <v>2.817875183725749</v>
+      </c>
+      <c r="C1705" t="n">
+        <v>2.890606431232979</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>1.556629079393153</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>3.512901638676493</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>2.164737430297627</v>
+      </c>
+      <c r="G1705" t="n">
+        <v>4.189448889411556</v>
       </c>
     </row>
   </sheetData>
